--- a/static/excel/FDX_model.xlsx
+++ b/static/excel/FDX_model.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Cover" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="P&amp;L" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Balance Sheet" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Cash Flow" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Ratios &amp; FCF" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Segments" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="WACC" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="DCF" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Scorecard" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cover" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="P&amp;L" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ratios &amp; FCF" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Segments" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WACC" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="DCF" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Scorecard" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -39,7 +39,7 @@
     <numFmt numFmtId="175" formatCode="0.000"/>
     <numFmt numFmtId="176" formatCode="0.00;(0.00);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="35">
+  <fonts count="36">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -216,7 +216,7 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00E65100"/>
+      <color rgb="00B71C1C"/>
       <sz val="10"/>
     </font>
     <font>
@@ -228,7 +228,13 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00B71C1C"/>
+      <color rgb="00E65100"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="001B5E20"/>
       <sz val="10"/>
     </font>
     <font>
@@ -331,7 +337,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE0B2"/>
+        <fgColor rgb="00FFCDD2"/>
       </patternFill>
     </fill>
     <fill>
@@ -341,7 +347,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFCDD2"/>
+        <fgColor rgb="00FFE0B2"/>
       </patternFill>
     </fill>
   </fills>
@@ -371,7 +377,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="143">
+  <cellXfs count="144">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -773,6 +779,9 @@
     <xf numFmtId="0" fontId="32" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="33" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -780,13 +789,13 @@
     <xf numFmtId="2" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="35" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
@@ -7344,11 +7353,11 @@
         </is>
       </c>
       <c r="B5" s="43" t="n">
-        <v>90665.795145</v>
+        <v>94058.783215</v>
       </c>
       <c r="C5" s="44" t="inlineStr">
         <is>
-          <t>FMP marketCap  |  price $379.98</t>
+          <t>FMP marketCap  |  price $394.2</t>
         </is>
       </c>
     </row>
@@ -7430,11 +7439,11 @@
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>0.0446</v>
+        <v>0.0457</v>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-13</t>
+          <t>FRED series DGS10  |  latest: 2026-05-21</t>
         </is>
       </c>
     </row>
@@ -7445,7 +7454,7 @@
         </is>
       </c>
       <c r="B13" s="48" t="n">
-        <v>0.0446</v>
+        <v>0.0457</v>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
@@ -7513,11 +7522,11 @@
     <row r="19">
       <c r="A19" s="17" t="inlineStr">
         <is>
-          <t>Damodaran re-levered  (D/E = 0.23x,  t = 24.8%)</t>
+          <t>Damodaran re-levered  (D/E = 0.22x,  t = 24.8%)</t>
         </is>
       </c>
       <c r="B19" s="50" t="n">
-        <v>1.171</v>
+        <v>1.165</v>
       </c>
       <c r="C19" s="44">
         <f> unlevered × (1 + (1 − t) × D/E)</f>
@@ -7531,7 +7540,7 @@
         </is>
       </c>
       <c r="B20" s="51" t="n">
-        <v>1.226</v>
+        <v>1.224</v>
       </c>
       <c r="C20" s="49" t="inlineStr">
         <is>
@@ -7705,11 +7714,11 @@
         </is>
       </c>
       <c r="B35" s="46" t="n">
-        <v>0.0542</v>
+        <v>0.0553</v>
       </c>
       <c r="C35" s="44" t="inlineStr">
         <is>
-          <t>Rf 4.46% + spread 0.96%</t>
+          <t>Rf 4.57% + spread 0.96%</t>
         </is>
       </c>
     </row>
@@ -7735,7 +7744,7 @@
         </is>
       </c>
       <c r="B37" s="48" t="n">
-        <v>0.0464</v>
+        <v>0.047</v>
       </c>
       <c r="C37" s="49" t="inlineStr">
         <is>
@@ -7800,16 +7809,16 @@
     <row r="44" ht="22" customHeight="1">
       <c r="A44" s="54" t="inlineStr">
         <is>
-          <t>WACC  =  (E/V × Re)  +  (D/V × Rd × (1 − t))</t>
+          <t>WACC  =  MAX(8.5%, (E/V × Re) + (D/V × Rd × (1 − t)))</t>
         </is>
       </c>
       <c r="B44" s="55">
-        <f>B8*B28+B9*B37*(1-B41)</f>
+        <f>MAX(0.085, B8*B28+B9*B37*(1-B41))</f>
         <v/>
       </c>
       <c r="C44" s="56" t="inlineStr">
         <is>
-          <t>Used as discount rate in DCF tab</t>
+          <t>Floored 8.5% (D-001); raw formula below</t>
         </is>
       </c>
     </row>
@@ -8172,13 +8181,13 @@
         <v/>
       </c>
       <c r="G7" s="71" t="n">
-        <v>0.064</v>
+        <v>0.0645</v>
       </c>
       <c r="H7" s="71" t="n">
-        <v>0.0497</v>
+        <v>0.0501</v>
       </c>
       <c r="I7" s="71" t="n">
-        <v>0.0479</v>
+        <v>0.0468</v>
       </c>
       <c r="J7" s="72">
         <f>I7</f>
@@ -8522,13 +8531,13 @@
         <v/>
       </c>
       <c r="G15" s="77" t="n">
-        <v>93549.7</v>
+        <v>93597.5</v>
       </c>
       <c r="H15" s="77" t="n">
-        <v>98200</v>
+        <v>98284</v>
       </c>
       <c r="I15" s="77" t="n">
-        <v>102899.7</v>
+        <v>102886.5</v>
       </c>
       <c r="J15" s="78">
         <f>I15*(1+J7)</f>
@@ -8556,27 +8565,27 @@
       </c>
       <c r="G16" s="82" t="inlineStr">
         <is>
-          <t>92,737 — 94,442</t>
+          <t>92,735 — 94,400</t>
         </is>
       </c>
       <c r="H16" s="82" t="inlineStr">
         <is>
-          <t>96,600 — 100,182</t>
+          <t>96,683 — 100,268</t>
         </is>
       </c>
       <c r="I16" s="82" t="inlineStr">
         <is>
-          <t>102,751 — 103,048</t>
+          <t>102,841 — 102,932</t>
         </is>
       </c>
       <c r="J16" s="82" t="inlineStr">
         <is>
-          <t>105,460 — 109,255</t>
+          <t>105,706 — 109,296</t>
         </is>
       </c>
       <c r="K16" s="82" t="inlineStr">
         <is>
-          <t>110,308 — 114,277</t>
+          <t>110,565 — 114,320</t>
         </is>
       </c>
       <c r="L16" s="83" t="inlineStr">
@@ -8720,13 +8729,13 @@
         <v/>
       </c>
       <c r="G20" s="77" t="n">
-        <v>11101.4</v>
+        <v>11107.1</v>
       </c>
       <c r="H20" s="77" t="n">
-        <v>11653.3</v>
+        <v>11663.2</v>
       </c>
       <c r="I20" s="77" t="n">
-        <v>12211</v>
+        <v>12209.4</v>
       </c>
       <c r="J20" s="78">
         <f>J15*J8</f>
@@ -8754,27 +8763,27 @@
       </c>
       <c r="G21" s="82" t="inlineStr">
         <is>
-          <t>11,005 — 11,207</t>
+          <t>11,005 — 11,202</t>
         </is>
       </c>
       <c r="H21" s="82" t="inlineStr">
         <is>
-          <t>11,463 — 11,889</t>
+          <t>11,473 — 11,899</t>
         </is>
       </c>
       <c r="I21" s="82" t="inlineStr">
         <is>
-          <t>12,193 — 12,229</t>
+          <t>12,204 — 12,215</t>
         </is>
       </c>
       <c r="J21" s="82" t="inlineStr">
         <is>
-          <t>12,515 — 12,965</t>
+          <t>12,544 — 12,970</t>
         </is>
       </c>
       <c r="K21" s="82" t="inlineStr">
         <is>
-          <t>13,090 — 13,561</t>
+          <t>13,121 — 13,566</t>
         </is>
       </c>
       <c r="L21" s="83" t="inlineStr">
@@ -9954,7 +9963,7 @@
         </is>
       </c>
       <c r="B61" s="112" t="n">
-        <v>379.98</v>
+        <v>394.2</v>
       </c>
       <c r="C61" s="104" t="n"/>
       <c r="D61" s="104" t="n"/>
@@ -10054,7 +10063,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="114" t="inlineStr">
         <is>
-          <t>JS SCORECARD — FDX  |  Master Prompt v2  |  15 May 2026  |  Sector bucket: Stable Compounder</t>
+          <t>JS SCORECARD — FDX  |  Master Prompt v2  |  24 May 2026  |  Sector bucket: Stable Compounder</t>
         </is>
       </c>
     </row>
@@ -10187,16 +10196,16 @@
       </c>
       <c r="D9" s="130" t="inlineStr">
         <is>
-          <t>GM 21.6% ✗ (&gt;40%)  |  GM trend +0.0% ✗ (&gt;+1pp)  |  ROIC-WACC +7.7% ✓ (&gt;+5pp)  |  Rev consistency σ=6.1% ✓ (&lt;8%)  [2/4 indicators positive — proxy score]</t>
+          <t>GM 21.6% ✗ (&gt;40%)  |  GM trend +0.0% ✗ (&gt;+1pp)  |  ROIC-WACC +1.8% ✗ (&gt;+5pp)  |  Rev consistency σ=6.1% ✓ (&lt;8%)  [1/4 indicators positive — proxy score]</t>
         </is>
       </c>
       <c r="E9" s="131" t="inlineStr">
         <is>
-          <t>MOD-LOW</t>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F9" s="132" t="n">
-        <v>5</v>
+        <v>2.5</v>
       </c>
       <c r="G9" s="133">
         <f>IF(F9="",0,C9*F9*10)</f>
@@ -10204,7 +10213,7 @@
       </c>
       <c r="H9" s="134" t="inlineStr">
         <is>
-          <t>GM 21.6% ✗ (&gt;40%)  |  GM trend +0.0% ✗ (&gt;+1pp)  |  ROIC-WACC +7.7% ✓ (&gt;+5pp)  |  Rev consistency σ=6.1% ✓ (&lt;8%)  [2/4 indicators positive — proxy score]</t>
+          <t>GM 21.6% ✗ (&gt;40%)  |  GM trend +0.0% ✗ (&gt;+1pp)  |  ROIC-WACC +1.8% ✗ (&gt;+5pp)  |  Rev consistency σ=6.1% ✓ (&lt;8%)  [1/4 indicators positive — proxy score]</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10263,7 @@
       </c>
       <c r="D11" s="130" t="inlineStr">
         <is>
-          <t>ROIC trend -2.9% ✗ (≥-2pp)  |  GM maintained +0.0% ✓  |  Op margin -0.1% ✓ (≥-2pp)  |  Capital returns MOD-HIGH ✓  |  Share count -2.1%/yr ✓ (net buyback)  |  Goodwill/Equity 24% ✓ (&lt;40%)  [5/6 indicators positive — proxy score]</t>
+          <t>ROIC trend -2.9% ✗ (&gt;=-2pp)  |  GM maintained +0.0% ✓  |  Op margin -0.1% ✓ (≥-2pp)  |  Capital returns MOD-HIGH ✓  |  Share count -2.1%/yr ✓ (net buyback)  |  Goodwill/Equity 24% ✓ (&lt;40%)  [5/6 indicators positive — proxy score]</t>
         </is>
       </c>
       <c r="E11" s="135" t="inlineStr">
@@ -10271,7 +10280,7 @@
       </c>
       <c r="H11" s="134" t="inlineStr">
         <is>
-          <t>ROIC trend -2.9% ✗ (≥-2pp)  |  GM maintained +0.0% ✓  |  Op margin -0.1% ✓ (≥-2pp)  |  Capital returns MOD-HIGH ✓  |  Share count -2.1%/yr ✓ (net buyback)  |  Goodwill/Equity 24% ✓ (&lt;40%)  [5/6 indicators positive — proxy score]</t>
+          <t>ROIC trend -2.9% ✗ (&gt;=-2pp)  |  GM maintained +0.0% ✓  |  Op margin -0.1% ✓ (≥-2pp)  |  Capital returns MOD-HIGH ✓  |  Share count -2.1%/yr ✓ (net buyback)  |  Goodwill/Equity 24% ✓ (&lt;40%)  [5/6 indicators positive — proxy score]</t>
         </is>
       </c>
     </row>
@@ -10301,7 +10310,7 @@
           <t>-2.0%</t>
         </is>
       </c>
-      <c r="E13" s="136" t="inlineStr">
+      <c r="E13" s="131" t="inlineStr">
         <is>
           <t>LOW</t>
         </is>
@@ -10412,7 +10421,7 @@
           <t>10.8%</t>
         </is>
       </c>
-      <c r="E16" s="131" t="inlineStr">
+      <c r="E16" s="136" t="inlineStr">
         <is>
           <t>MOD-LOW</t>
         </is>
@@ -10527,7 +10536,7 @@
       </c>
       <c r="D20" s="130" t="inlineStr">
         <is>
-          <t>Rev growth σ=6.1%  |  Op margin σ=0.5%  [proxy — lower σ = lower risk = higher score]</t>
+          <t>Rev growth σ=6.1%  |  OM trend -0.3%, σ=0.5%  [quality = direction + stability]</t>
         </is>
       </c>
       <c r="E20" s="135" t="inlineStr">
@@ -10536,7 +10545,7 @@
         </is>
       </c>
       <c r="F20" s="132" t="n">
-        <v>8.33</v>
+        <v>6.67</v>
       </c>
       <c r="G20" s="133">
         <f>IF(F20="",0,C20*F20*10)</f>
@@ -10544,7 +10553,7 @@
       </c>
       <c r="H20" s="134" t="inlineStr">
         <is>
-          <t>Rev growth σ=6.1%  |  Op margin σ=0.5%  [proxy — lower σ = lower risk = higher score]</t>
+          <t>Rev growth σ=6.1%  |  OM trend -0.3%, σ=0.5%  [quality = direction + stability]</t>
         </is>
       </c>
     </row>
@@ -10571,16 +10580,16 @@
       </c>
       <c r="D22" s="130" t="inlineStr">
         <is>
-          <t>Current 13.0x  |  5yr avg 14.5x  |  DCF-implied 12.4x  [+5% vs benchmark]</t>
-        </is>
-      </c>
-      <c r="E22" s="135" t="inlineStr">
-        <is>
-          <t>MOD-HIGH</t>
+          <t>Current 13.0x  |  5yr avg 14.5x  |  DCF-implied 12.1x [ref only — not used as benchmark]  [-10% vs benchmark]  [trail=8.55 | fwd_pe=19.9x→1.53 | abs=12.0 → blended 40/40/20=6.43]  PEG=113.66 (fwd_pe=19.9x / eps_growth=18%)  [revision:Modest upgrade expected→+0.25]</t>
+        </is>
+      </c>
+      <c r="E22" s="137" t="inlineStr">
+        <is>
+          <t>HIGH</t>
         </is>
       </c>
       <c r="F22" s="132" t="n">
-        <v>6.23</v>
+        <v>6.68</v>
       </c>
       <c r="G22" s="133">
         <f>IF(F22="",0,C22*F22*10)</f>
@@ -10588,7 +10597,7 @@
       </c>
       <c r="H22" s="134" t="inlineStr">
         <is>
-          <t>Current 13.0x  |  5yr avg 14.5x  |  DCF-implied 12.4x  [+5% vs benchmark]</t>
+          <t>Current 13.0x  |  5yr avg 14.5x  |  DCF-implied 12.1x [ref only — not used as benchmark]  [-10% vs benchmark]  [trail=8.55 | fwd_pe=19.9x→1.53 | abs=12.0 → blended 40/40/20=6.43]  PEG=113.66 (fwd_pe=19.9x / eps_growth=18%)  [revision:Modest upgrade expected→+0.25]</t>
         </is>
       </c>
     </row>
@@ -10608,7 +10617,7 @@
       </c>
       <c r="D23" s="130" t="inlineStr">
         <is>
-          <t>Current 17.8x  |  5yr avg 19.5x  |  DCF-implied 17.0x  [+5% vs benchmark]</t>
+          <t>Current 17.8x  |  5yr avg 19.5x  |  DCF-implied 16.6x [ref only — not used as benchmark]  [-9% vs benchmark]  [trail=8.31 | fwd_pfcf=30.2x→0.00 | abs=10.0 → blended 40/40/20=5.32]</t>
         </is>
       </c>
       <c r="E23" s="135" t="inlineStr">
@@ -10617,7 +10626,7 @@
         </is>
       </c>
       <c r="F23" s="132" t="n">
-        <v>6.25</v>
+        <v>5.32</v>
       </c>
       <c r="G23" s="133">
         <f>IF(F23="",0,C23*F23*10)</f>
@@ -10625,7 +10634,7 @@
       </c>
       <c r="H23" s="134" t="inlineStr">
         <is>
-          <t>Current 17.8x  |  5yr avg 19.5x  |  DCF-implied 17.0x  [+5% vs benchmark]</t>
+          <t>Current 17.8x  |  5yr avg 19.5x  |  DCF-implied 16.6x [ref only — not used as benchmark]  [-9% vs benchmark]  [trail=8.31 | fwd_pfcf=30.2x→0.00 | abs=10.0 → blended 40/40/20=5.32]</t>
         </is>
       </c>
     </row>
@@ -10640,21 +10649,21 @@
       <c r="H24" s="42" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="137" t="inlineStr">
+      <c r="A25" s="138" t="inlineStr">
         <is>
           <t>TOTAL SCORE  (max = 100.0)</t>
         </is>
       </c>
-      <c r="B25" s="138" t="n"/>
-      <c r="C25" s="138" t="n"/>
-      <c r="D25" s="138" t="n"/>
-      <c r="E25" s="138" t="n"/>
-      <c r="F25" s="138" t="n"/>
-      <c r="G25" s="139">
+      <c r="B25" s="139" t="n"/>
+      <c r="C25" s="139" t="n"/>
+      <c r="D25" s="139" t="n"/>
+      <c r="E25" s="139" t="n"/>
+      <c r="F25" s="139" t="n"/>
+      <c r="G25" s="140">
         <f>G8+G9+G10+G11+G13+G14+G15+G16+G18+G19+G20+G22+G23</f>
         <v/>
       </c>
-      <c r="H25" s="140" t="inlineStr">
+      <c r="H25" s="141" t="inlineStr">
         <is>
           <t>No floor cap.</t>
         </is>
@@ -10671,7 +10680,7 @@
       <c r="H26" s="42" t="n"/>
     </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="141">
+      <c r="A27" s="142">
         <f>IF(G25="","Score incomplete — fill qualitative tiers above",IF(G25&gt;=80,"STRONG BUY",IF(G25&gt;=65,"BUY",IF(G25&gt;=50,"HOLD",IF(G25&gt;=35,"REDUCE","SELL")))))</f>
         <v/>
       </c>
@@ -10687,7 +10696,7 @@
       <c r="H28" s="42" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="142" t="inlineStr">
+      <c r="A29" s="143" t="inlineStr">
         <is>
           <t>SCORING GUIDE:  ≥80 STRONG BUY  |  65–79 BUY  |  50–64 HOLD  |  35–49 REDUCE  |  &lt;35 SELL    ||  Soft cap (non-banks only): −5pts per 1.0x of D/EBITDA above 3.0x; −4pts per 1.0x of EBIT/Int below 3.0x; min 40    ||  Banks: gates exempt; P3 uses Equity/Assets (CET1 proxy) instead of D/EBITDA</t>
         </is>

--- a/static/excel/FDX_model.xlsx
+++ b/static/excel/FDX_model.xlsx
@@ -39,7 +39,7 @@
     <numFmt numFmtId="175" formatCode="0.000"/>
     <numFmt numFmtId="176" formatCode="0.00;(0.00);&quot;-&quot;"/>
   </numFmts>
-  <fonts count="36">
+  <fonts count="35">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -233,12 +233,6 @@
     </font>
     <font>
       <name val="Arial"/>
-      <b val="1"/>
-      <color rgb="001B5E20"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="Arial"/>
       <color rgb="001B5E20"/>
       <sz val="10"/>
     </font>
@@ -377,7 +371,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="144">
+  <cellXfs count="143">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
@@ -779,9 +773,6 @@
     <xf numFmtId="0" fontId="32" fillId="20" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="33" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
@@ -789,13 +780,13 @@
     <xf numFmtId="2" fontId="12" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="34" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="33" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="35" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="2"/>
     </xf>
   </cellXfs>
@@ -7439,11 +7430,11 @@
         </is>
       </c>
       <c r="B12" s="46" t="n">
-        <v>0.0457</v>
+        <v>0.04559999999999999</v>
       </c>
       <c r="C12" s="44" t="inlineStr">
         <is>
-          <t>FRED series DGS10  |  latest: 2026-05-21</t>
+          <t>FRED series DGS10  |  latest: 2026-05-22</t>
         </is>
       </c>
     </row>
@@ -7454,7 +7445,7 @@
         </is>
       </c>
       <c r="B13" s="48" t="n">
-        <v>0.0457</v>
+        <v>0.0456</v>
       </c>
       <c r="C13" s="49" t="inlineStr">
         <is>
@@ -7653,25 +7644,27 @@
       </c>
       <c r="B31" s="53" t="inlineStr">
         <is>
-          <t>Not available</t>
+          <t>BBB</t>
         </is>
       </c>
       <c r="C31" s="44" t="inlineStr">
         <is>
-          <t>FMP /ratings endpoint</t>
+          <t>User input</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="17" t="inlineStr">
         <is>
-          <t>FRED matched yield</t>
-        </is>
-      </c>
-      <c r="B32" s="53" t="n"/>
+          <t>FRED matched yield  (rating-tier index)</t>
+        </is>
+      </c>
+      <c r="B32" s="46" t="n">
+        <v>0.0539</v>
+      </c>
       <c r="C32" s="44" t="inlineStr">
         <is>
-          <t>No rating returned — FRED method not applicable</t>
+          <t>FRED BAMLC0A4CBBBEY — BBB</t>
         </is>
       </c>
     </row>
@@ -7714,11 +7707,11 @@
         </is>
       </c>
       <c r="B35" s="46" t="n">
-        <v>0.0553</v>
+        <v>0.05519999999999999</v>
       </c>
       <c r="C35" s="44" t="inlineStr">
         <is>
-          <t>Rf 4.57% + spread 0.96%</t>
+          <t>Rf 4.56% + spread 0.96%</t>
         </is>
       </c>
     </row>
@@ -7744,11 +7737,11 @@
         </is>
       </c>
       <c r="B37" s="48" t="n">
-        <v>0.047</v>
+        <v>0.0493</v>
       </c>
       <c r="C37" s="49" t="inlineStr">
         <is>
-          <t>Default = average of 2 source(s) above — override freely</t>
+          <t>Default = average of 3 source(s) above — override freely</t>
         </is>
       </c>
     </row>
@@ -10063,7 +10056,7 @@
     <row r="1" ht="18" customHeight="1">
       <c r="A1" s="114" t="inlineStr">
         <is>
-          <t>JS SCORECARD — FDX  |  Master Prompt v2  |  24 May 2026  |  Sector bucket: Stable Compounder</t>
+          <t>JS SCORECARD — FDX  |  Master Prompt v2  |  27 May 2026  |  Sector bucket: Stable Compounder</t>
         </is>
       </c>
     </row>
@@ -10580,16 +10573,16 @@
       </c>
       <c r="D22" s="130" t="inlineStr">
         <is>
-          <t>Current 13.0x  |  5yr avg 14.5x  |  DCF-implied 12.1x [ref only — not used as benchmark]  [-10% vs benchmark]  [trail=8.55 | fwd_pe=19.9x→1.53 | abs=12.0 → blended 40/40/20=6.43]  PEG=113.66 (fwd_pe=19.9x / eps_growth=18%)  [revision:Modest upgrade expected→+0.25]</t>
-        </is>
-      </c>
-      <c r="E22" s="137" t="inlineStr">
-        <is>
-          <t>HIGH</t>
+          <t>Fwd P/E 19.9x (scoring basis)  |  5yr avg 14.2x  |  DCF-implied 12.0x [ref only — not used as benchmark]  [+40% vs benchmark]  [trail=1.18 | fwd_pe=19.9x→1.18 | abs=10.0 → blended 40/40/20=2.95]  PEG=113.66 (fwd_pe=19.9x / eps_growth=18%)  [revision:Modest upgrade expected→+0.25]</t>
+        </is>
+      </c>
+      <c r="E22" s="131" t="inlineStr">
+        <is>
+          <t>LOW</t>
         </is>
       </c>
       <c r="F22" s="132" t="n">
-        <v>6.68</v>
+        <v>3.2</v>
       </c>
       <c r="G22" s="133">
         <f>IF(F22="",0,C22*F22*10)</f>
@@ -10597,7 +10590,7 @@
       </c>
       <c r="H22" s="134" t="inlineStr">
         <is>
-          <t>Current 13.0x  |  5yr avg 14.5x  |  DCF-implied 12.1x [ref only — not used as benchmark]  [-10% vs benchmark]  [trail=8.55 | fwd_pe=19.9x→1.53 | abs=12.0 → blended 40/40/20=6.43]  PEG=113.66 (fwd_pe=19.9x / eps_growth=18%)  [revision:Modest upgrade expected→+0.25]</t>
+          <t>Fwd P/E 19.9x (scoring basis)  |  5yr avg 14.2x  |  DCF-implied 12.0x [ref only — not used as benchmark]  [+40% vs benchmark]  [trail=1.18 | fwd_pe=19.9x→1.18 | abs=10.0 → blended 40/40/20=2.95]  PEG=113.66 (fwd_pe=19.9x / eps_growth=18%)  [revision:Modest upgrade expected→+0.25]</t>
         </is>
       </c>
     </row>
@@ -10617,7 +10610,7 @@
       </c>
       <c r="D23" s="130" t="inlineStr">
         <is>
-          <t>Current 17.8x  |  5yr avg 19.5x  |  DCF-implied 16.6x [ref only — not used as benchmark]  [-9% vs benchmark]  [trail=8.31 | fwd_pfcf=30.2x→0.00 | abs=10.0 → blended 40/40/20=5.32]</t>
+          <t>Current 17.8x  |  5yr avg 19.2x  |  DCF-implied 16.5x [ref only — not used as benchmark]  [-7% vs benchmark]  [trail=8.09 | fwd_pfcf=30.2x→0.00 | abs=10.0 → blended 40/40/20=5.24]</t>
         </is>
       </c>
       <c r="E23" s="135" t="inlineStr">
@@ -10626,7 +10619,7 @@
         </is>
       </c>
       <c r="F23" s="132" t="n">
-        <v>5.32</v>
+        <v>5.24</v>
       </c>
       <c r="G23" s="133">
         <f>IF(F23="",0,C23*F23*10)</f>
@@ -10634,7 +10627,7 @@
       </c>
       <c r="H23" s="134" t="inlineStr">
         <is>
-          <t>Current 17.8x  |  5yr avg 19.5x  |  DCF-implied 16.6x [ref only — not used as benchmark]  [-9% vs benchmark]  [trail=8.31 | fwd_pfcf=30.2x→0.00 | abs=10.0 → blended 40/40/20=5.32]</t>
+          <t>Current 17.8x  |  5yr avg 19.2x  |  DCF-implied 16.5x [ref only — not used as benchmark]  [-7% vs benchmark]  [trail=8.09 | fwd_pfcf=30.2x→0.00 | abs=10.0 → blended 40/40/20=5.24]</t>
         </is>
       </c>
     </row>
@@ -10649,21 +10642,21 @@
       <c r="H24" s="42" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="138" t="inlineStr">
+      <c r="A25" s="137" t="inlineStr">
         <is>
           <t>TOTAL SCORE  (max = 100.0)</t>
         </is>
       </c>
-      <c r="B25" s="139" t="n"/>
-      <c r="C25" s="139" t="n"/>
-      <c r="D25" s="139" t="n"/>
-      <c r="E25" s="139" t="n"/>
-      <c r="F25" s="139" t="n"/>
-      <c r="G25" s="140">
+      <c r="B25" s="138" t="n"/>
+      <c r="C25" s="138" t="n"/>
+      <c r="D25" s="138" t="n"/>
+      <c r="E25" s="138" t="n"/>
+      <c r="F25" s="138" t="n"/>
+      <c r="G25" s="139">
         <f>G8+G9+G10+G11+G13+G14+G15+G16+G18+G19+G20+G22+G23</f>
         <v/>
       </c>
-      <c r="H25" s="141" t="inlineStr">
+      <c r="H25" s="140" t="inlineStr">
         <is>
           <t>No floor cap.</t>
         </is>
@@ -10680,7 +10673,7 @@
       <c r="H26" s="42" t="n"/>
     </row>
     <row r="27" ht="24" customHeight="1">
-      <c r="A27" s="142">
+      <c r="A27" s="141">
         <f>IF(G25="","Score incomplete — fill qualitative tiers above",IF(G25&gt;=80,"STRONG BUY",IF(G25&gt;=65,"BUY",IF(G25&gt;=50,"HOLD",IF(G25&gt;=35,"REDUCE","SELL")))))</f>
         <v/>
       </c>
@@ -10696,7 +10689,7 @@
       <c r="H28" s="42" t="n"/>
     </row>
     <row r="29" ht="18" customHeight="1">
-      <c r="A29" s="143" t="inlineStr">
+      <c r="A29" s="142" t="inlineStr">
         <is>
           <t>SCORING GUIDE:  ≥80 STRONG BUY  |  65–79 BUY  |  50–64 HOLD  |  35–49 REDUCE  |  &lt;35 SELL    ||  Soft cap (non-banks only): −5pts per 1.0x of D/EBITDA above 3.0x; −4pts per 1.0x of EBIT/Int below 3.0x; min 40    ||  Banks: gates exempt; P3 uses Equity/Assets (CET1 proxy) instead of D/EBITDA</t>
         </is>
